--- a/backend/wp_templates/D/D6 合同资产.xlsx
+++ b/backend/wp_templates/D/D6 合同资产.xlsx
@@ -25294,7 +25294,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="175">
-        <f>E12+SUM(H12:I12)-SUM(J12:L12)</f>
+        <f>K12+L12+M12</f>
         <v>0</v>
       </c>
     </row>
@@ -25453,7 +25453,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="175">
-        <f>E17+SUM(H17:I17)-SUM(J17:L17)</f>
+        <f>K17+L17+M17</f>
         <v>0</v>
       </c>
     </row>

--- a/backend/wp_templates/D/D6 合同资产.xlsx
+++ b/backend/wp_templates/D/D6 合同资产.xlsx
@@ -14889,7 +14889,7 @@
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="39">
-        <f t="shared" ref="F13:F17" si="1">B13-E13</f>
+        <f t="shared" ref="F13:F17" si="1">D13-E13</f>
         <v>0</v>
       </c>
       <c r="G13" s="40"/>
@@ -14968,11 +14968,11 @@
         <v>0</v>
       </c>
       <c r="C18" s="43">
-        <f>SUM(C13:C17)</f>
+        <f>IF(B18=0,"",D18/B18)</f>
         <v>0</v>
       </c>
       <c r="D18" s="44" t="str">
-        <f>IF(B18=0,"",C18/B18)</f>
+        <f>SUM(D13:D17)</f>
         <v/>
       </c>
       <c r="E18" s="43">
